--- a/data/trans_camb/P15B_3_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P15B_3_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-14,95</t>
+          <t>-15,61</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,44</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,04</t>
+          <t>-8,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 13,47</t>
+          <t>-26,95; 11,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 0,23</t>
+          <t>-40,55; 1,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 5,38</t>
+          <t>-35,66; 4,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 1,11</t>
+          <t>-16,02; 0,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 2,37</t>
+          <t>-14,73; 2,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 2,78</t>
+          <t>-14,02; 2,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 5,02</t>
+          <t>-15,08; 4,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,25; -0,74</t>
+          <t>-19,55; -0,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 0,58</t>
+          <t>-19,55; -0,37</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-51,52%</t>
+          <t>-53,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-50,51%</t>
+          <t>-52,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-54,62%</t>
+          <t>-56,68%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,29; 97,63</t>
+          <t>-61,68; 78,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-89,58; 12,42</t>
+          <t>-89,97; 25,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-86,33; 63,16</t>
+          <t>-85,87; 42,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,17; —</t>
+          <t>-93,2; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,23; 66,63</t>
+          <t>-66,19; 51,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 7,18</t>
+          <t>-89,2; -3,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-82,67; 13,4</t>
+          <t>-83,71; 7,13</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-8,41</t>
+          <t>-8,56</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-2,7</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-8,86</t>
+          <t>-9,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,56; -4,78</t>
+          <t>-28,9; -4,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-33,52; -6,37</t>
+          <t>-34,35; -7,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 6,63</t>
+          <t>-23,29; 5,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 3,16</t>
+          <t>-21,63; 3,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 6,08</t>
+          <t>-19,06; 5,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 9,13</t>
+          <t>-16,83; 7,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,75; -5,08</t>
+          <t>-24,8; -4,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,81; -7,06</t>
+          <t>-26,31; -5,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 1,39</t>
+          <t>-19,88; 1,04</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-22,47%</t>
+          <t>-22,86%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,86%</t>
+          <t>-19,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-29,36%</t>
+          <t>-30,31%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,74; -16,41</t>
+          <t>-62,62; -14,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,07; -20,68</t>
+          <t>-72,26; -19,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 23,88</t>
+          <t>-49,96; 21,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,68; 84,72</t>
+          <t>-85,34; 105,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,19; 131,36</t>
+          <t>-77,71; 139,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 206,78</t>
+          <t>-70,63; 136,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,36; -21,2</t>
+          <t>-65,82; -18,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,6; -29,74</t>
+          <t>-70,29; -21,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,3; 7,03</t>
+          <t>-54,22; 7,74</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,94</t>
+          <t>-7,31</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,21</t>
+          <t>-7,45</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,78</t>
+          <t>-7,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 23,58</t>
+          <t>-25,38; 26,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-39,17; 11,05</t>
+          <t>-36,47; 11,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 10,89</t>
+          <t>-32,85; 9,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 24,03</t>
+          <t>-29,74; 23,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,88; 17,29</t>
+          <t>-34,43; 16,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 6,46</t>
+          <t>-41,98; 6,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 18,56</t>
+          <t>-18,53; 18,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 11,14</t>
+          <t>-23,83; 10,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 5,41</t>
+          <t>-27,09; 4,62</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-41,12%</t>
+          <t>-50,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-62,71%</t>
+          <t>-64,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-51,14%</t>
+          <t>-56,82%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,39; —</t>
+          <t>-86,37; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-72,7; 665,79</t>
+          <t>-85,74; 406,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,1; —</t>
+          <t>-90,9; 445,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-99,87; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,2</t>
+          <t>-10,03</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,7</t>
+          <t>-8,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,19; -0,15</t>
+          <t>-20,47; -1,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-27,47; -7,76</t>
+          <t>-27,88; -8,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 2,3</t>
+          <t>-20,47; 0,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 1,39</t>
+          <t>-13,74; 1,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 4,11</t>
+          <t>-11,57; 3,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 3,53</t>
+          <t>-10,86; 3,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -2,85</t>
+          <t>-15,26; -1,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -5,02</t>
+          <t>-18,5; -4,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,19; -1,09</t>
+          <t>-14,5; -1,26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-28,68%</t>
+          <t>-31,27%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-26,58%</t>
+          <t>-29,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-34,09%</t>
+          <t>-36,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,99; -0,46</t>
+          <t>-52,76; -4,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,42; -30,78</t>
+          <t>-71,38; -30,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 10,75</t>
+          <t>-53,13; 4,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 34,13</t>
+          <t>-80,15; 37,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 82,98</t>
+          <t>-69,68; 67,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,17; 71,01</t>
+          <t>-68,0; 63,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,3; -14,83</t>
+          <t>-55,06; -8,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,38; -27,21</t>
+          <t>-67,12; -26,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,28; -5,13</t>
+          <t>-54,84; -7,06</t>
         </is>
       </c>
     </row>
